--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486919_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486919_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8049</v>
+        <v>6.9382</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2294</v>
+        <v>6.0663</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5755</v>
+        <v>0.8719</v>
       </c>
       <c r="G2" t="n">
         <v>3.6345</v>
@@ -610,13 +610,13 @@
         <v>2.0534</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2053</v>
+        <v>1.3386</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1358</v>
+        <v>0.701</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3411</v>
+        <v>0.6375999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>0.9384</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.2599</v>
+        <v>1.7683</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7962</v>
+        <v>4.4824</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.5362</v>
+        <v>-2.7141</v>
       </c>
       <c r="G3" t="n">
         <v>1.1003</v>
@@ -688,13 +688,13 @@
         <v>1.4374</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1247</v>
+        <v>1.6331</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5574</v>
+        <v>1.2435</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5674</v>
+        <v>0.3895</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3491</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1989</v>
+        <v>0.6892</v>
       </c>
       <c r="E4" t="n">
-        <v>2.1954</v>
+        <v>0.6264</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0035</v>
+        <v>0.06279999999999999</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8543</v>
@@ -766,13 +766,13 @@
         <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>3.8479</v>
+        <v>2.3382</v>
       </c>
       <c r="T4" t="n">
-        <v>3.2619</v>
+        <v>1.6929</v>
       </c>
       <c r="U4" t="n">
-        <v>0.586</v>
+        <v>0.6453</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3475</v>
+        <v>0.6623</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6281</v>
+        <v>0.2097</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7194</v>
+        <v>0.4526</v>
       </c>
       <c r="G5" t="n">
         <v>-0.5943000000000001</v>
@@ -844,13 +844,13 @@
         <v>1.4374</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6625</v>
+        <v>0.9772999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9413</v>
+        <v>0.5229</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7212</v>
+        <v>0.4544</v>
       </c>
       <c r="V5" t="n">
         <v>-0.1314</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3408</v>
+        <v>0.1299</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5898</v>
+        <v>2.1714</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.249</v>
+        <v>-2.0415</v>
       </c>
       <c r="G6" t="n">
         <v>-0.3915</v>
@@ -922,13 +922,13 @@
         <v>2.4641</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3936</v>
+        <v>1.1826</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9218</v>
+        <v>0.5034</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4718</v>
+        <v>0.6792</v>
       </c>
       <c r="V6" t="n">
         <v>2.0082</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.2502</v>
+        <v>-1.5675</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.9291</v>
+        <v>-1.1658</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3211</v>
+        <v>-0.4018</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3395</v>
+        <v>-1.7376</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.6471</v>
+        <v>-0.9245</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3077</v>
+        <v>-0.8131</v>
       </c>
       <c r="J7" t="n">
-        <v>2.4526</v>
+        <v>-1.3168</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8483000000000001</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6043</v>
+        <v>-0.6974</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.7921</v>
+        <v>-0.4208</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4955</v>
+        <v>-0.305</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.2966</v>
+        <v>-0.1157</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2588</v>
+        <v>0.4107</v>
       </c>
       <c r="Q7" t="n">
-        <v>-5.1336</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.8748</v>
+        <v>0.4107</v>
       </c>
       <c r="S7" t="n">
-        <v>1.8676</v>
+        <v>0.3487</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0927</v>
+        <v>0.1511</v>
       </c>
       <c r="U7" t="n">
-        <v>1.7749</v>
+        <v>0.1976</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4805</v>
+        <v>-0.5893</v>
       </c>
       <c r="W7" t="n">
-        <v>1.6591</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8953</v>
+        <v>-1.7384</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.375</v>
+        <v>-0.8245</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5203</v>
+        <v>-0.9139</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.7376</v>
+        <v>-1.3395</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9245</v>
+        <v>-1.6471</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8131</v>
+        <v>0.3077</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.3168</v>
+        <v>2.4526</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6195000000000001</v>
+        <v>0.8483000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6974</v>
+        <v>1.6043</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4208</v>
+        <v>-3.7921</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.305</v>
+        <v>-2.4955</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1157</v>
+        <v>-1.2966</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-5.1336</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>2.8748</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0209</v>
+        <v>1.3793</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0581</v>
+        <v>0.1973</v>
       </c>
       <c r="U8" t="n">
-        <v>0.079</v>
+        <v>1.182</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.5893</v>
+        <v>0.4805</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.6591</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5893</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1216</v>
+        <v>-2.0746</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9825</v>
+        <v>-1.6686</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1391</v>
+        <v>-0.4059</v>
       </c>
       <c r="G9" t="n">
         <v>-1.444</v>
@@ -1156,13 +1156,13 @@
         <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>1.7865</v>
+        <v>1.8335</v>
       </c>
       <c r="T9" t="n">
-        <v>0.6933</v>
+        <v>1.0071</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0932</v>
+        <v>0.8264</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.046</v>
+        <v>-2.1683</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.3762</v>
+        <v>-3.121</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3302</v>
+        <v>0.9527</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1096</v>
@@ -1234,13 +1234,13 @@
         <v>1.8481</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.9179</v>
+        <v>0.9598</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4961</v>
+        <v>0.7592</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4218</v>
+        <v>0.2007</v>
       </c>
       <c r="V10" t="n">
         <v>0.2402</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>2.6389</v>
+        <v>2.6391</v>
       </c>
       <c r="E11" t="n">
-        <v>6.7761</v>
+        <v>6.776300000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.1371</v>
+        <v>-4.1372</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.735999999999999</v>
+        <v>-3.736</v>
       </c>
       <c r="H11" t="n">
         <v>-4.3146</v>
@@ -1318,13 +1318,13 @@
         <v>6.7784</v>
       </c>
       <c r="U11" t="n">
-        <v>5.2128</v>
+        <v>5.212700000000001</v>
       </c>
       <c r="V11" t="n">
         <v>2.5975</v>
       </c>
       <c r="W11" t="n">
-        <v>9.954499999999999</v>
+        <v>9.954500000000001</v>
       </c>
       <c r="X11" t="n">
         <v>-7.357100000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>8.126200000000001</v>
+        <v>8.520200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>4.4362</v>
+        <v>4.75</v>
       </c>
       <c r="F12" t="n">
-        <v>3.69</v>
+        <v>3.7702</v>
       </c>
       <c r="G12" t="n">
         <v>8.5092</v>
@@ -1390,13 +1390,13 @@
         <v>3.4908</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0894</v>
+        <v>-0.6954</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9726</v>
+        <v>-0.6588000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1168</v>
+        <v>-0.0366</v>
       </c>
       <c r="V12" t="n">
         <v>1.5277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.6142</v>
+        <v>5.0343</v>
       </c>
       <c r="E13" t="n">
-        <v>4.8199</v>
+        <v>5.0291</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2057</v>
+        <v>0.0052</v>
       </c>
       <c r="G13" t="n">
         <v>3.1097</v>
@@ -1468,13 +1468,13 @@
         <v>3.2855</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.3354</v>
+        <v>-0.9153</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0308</v>
+        <v>-0.8216</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3046</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-0.2402</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1573</v>
+        <v>1.6106</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0468</v>
+        <v>1.3606</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1105</v>
+        <v>0.25</v>
       </c>
       <c r="G14" t="n">
         <v>2.4831</v>
@@ -1546,13 +1546,13 @@
         <v>2.2588</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.3792</v>
+        <v>-0.926</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1121</v>
+        <v>-0.7983</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2672</v>
+        <v>-0.1277</v>
       </c>
       <c r="V14" t="n">
         <v>-1.1786</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6506</v>
+        <v>-0.9637</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7937</v>
+        <v>-1.5845</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1431</v>
+        <v>0.6208</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7727000000000001</v>
@@ -1702,13 +1702,13 @@
         <v>2.6694</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.4056</v>
+        <v>-0.7187</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5192</v>
+        <v>-0.31</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8863</v>
+        <v>-0.4087</v>
       </c>
       <c r="V16" t="n">
         <v>0.9384</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. MUKENDI MUKENDI</t>
+          <t>F. HERNANDEZ MARTINEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2225</v>
+        <v>-1.5335</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.3009</v>
+        <v>0.8585</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.9215</v>
+        <v>-2.3919</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.7258</v>
+        <v>-1.9693</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.771</v>
+        <v>-1.9271</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9549</v>
+        <v>-0.0421</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.977</v>
+        <v>1.4894</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.1348</v>
+        <v>-0.2073</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1579</v>
+        <v>1.6967</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7489</v>
+        <v>-3.4586</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6362</v>
+        <v>-1.7198</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.1127</v>
+        <v>-1.7388</v>
       </c>
       <c r="P17" t="n">
+        <v>1.8481</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.0267</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.2588</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.2321</v>
+        <v>2.8748</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2426</v>
+        <v>-1.4123</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0118</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2544</v>
+        <v>-0.6294</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2875</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.9466</v>
+        <v>1.1786</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.6591</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.3303</v>
+        <v>-1.5596</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7694</v>
+        <v>-0.4555</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5609</v>
+        <v>-1.1041</v>
       </c>
       <c r="G18" t="n">
         <v>-2.1229</v>
@@ -1858,13 +1858,13 @@
         <v>2.0534</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.9117</v>
+        <v>-1.1411</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6355</v>
+        <v>-0.3217</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.2761</v>
+        <v>-0.8193</v>
       </c>
       <c r="V18" t="n">
         <v>-0.3491</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. TOLEDO ZAMORA</t>
+          <t>R. TIMONER GIMENEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.455</v>
+        <v>-1.7152</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6675</v>
+        <v>-1.5854</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7875</v>
+        <v>-0.1298</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6114000000000001</v>
+        <v>-1.0138</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6195000000000001</v>
+        <v>-1.4664</v>
       </c>
       <c r="I19" t="n">
-        <v>0.008</v>
+        <v>0.4525</v>
       </c>
       <c r="J19" t="n">
-        <v>0.06619999999999999</v>
+        <v>1.6655</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0137</v>
+        <v>-0.0837</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0525</v>
+        <v>1.7492</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6776</v>
+        <v>-2.6793</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6332</v>
+        <v>-1.3827</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0445</v>
+        <v>-1.2966</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.2053</v>
+        <v>1.2321</v>
       </c>
       <c r="Q19" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0534</v>
+        <v>3.4908</v>
       </c>
       <c r="S19" t="n">
-        <v>1.0456</v>
+        <v>-1.6932</v>
       </c>
       <c r="T19" t="n">
-        <v>1.6114</v>
+        <v>-0.9921</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5659</v>
+        <v>-0.701</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.6838</v>
+        <v>-0.2402</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.0863</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.5975</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. HERNANDEZ MARTINEZ</t>
+          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.583</v>
+        <v>-2.2678</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5446</v>
+        <v>-1.4037</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.1277</v>
+        <v>-0.8641</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.9693</v>
+        <v>-0.9749</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9271</v>
+        <v>-0.1882</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0421</v>
+        <v>-0.7866</v>
       </c>
       <c r="J20" t="n">
-        <v>1.4894</v>
+        <v>-1.1595</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.2073</v>
+        <v>-0.5806</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6967</v>
+        <v>-0.579</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.4586</v>
+        <v>0.1846</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7198</v>
+        <v>0.3923</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.7388</v>
+        <v>-0.2077</v>
       </c>
       <c r="P20" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.8748</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.4618</v>
+        <v>-0.6606</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0966</v>
+        <v>-0.2442</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3652</v>
+        <v>-0.4164</v>
       </c>
       <c r="V20" t="n">
+        <v>-1.6591</v>
+      </c>
+      <c r="W20" t="n">
         <v>0</v>
       </c>
-      <c r="W20" t="n">
-        <v>1.1786</v>
-      </c>
       <c r="X20" t="n">
-        <v>-1.1786</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R. TIMONER GIMENEZ</t>
+          <t>M. MUKENDI MUKENDI</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6288</v>
+        <v>-2.5677</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5854</v>
+        <v>-0.5101</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0434</v>
+        <v>-2.0576</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.0138</v>
+        <v>-2.7258</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.4664</v>
+        <v>-1.771</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4525</v>
+        <v>-0.9549</v>
       </c>
       <c r="J21" t="n">
-        <v>1.6655</v>
+        <v>-0.977</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0837</v>
+        <v>-1.1348</v>
       </c>
       <c r="L21" t="n">
-        <v>1.7492</v>
+        <v>0.1579</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6793</v>
+        <v>-1.7489</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3827</v>
+        <v>-0.6362</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2966</v>
+        <v>-1.1127</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R21" t="n">
-        <v>3.4908</v>
+        <v>1.2321</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.6067</v>
+        <v>-0.1027</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9921</v>
+        <v>-0.221</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.6146</v>
+        <v>0.1183</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2402</v>
+        <v>1.2875</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.9466</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2402</v>
+        <v>-1.6591</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>R. MARTÍNEZ-QUINTANILLA JIMÉNEZ</t>
+          <t>C. TOLEDO ZAMORA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.6967</v>
+        <v>-3.7399</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6129</v>
+        <v>-2.3411</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0838</v>
+        <v>-1.3988</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.9749</v>
+        <v>-0.6114000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1882</v>
+        <v>-0.6195000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7866</v>
+        <v>0.008</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1595</v>
+        <v>0.06619999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.5806</v>
+        <v>0.0137</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.579</v>
+        <v>0.0525</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1846</v>
+        <v>-0.6776</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3923</v>
+        <v>-0.6332</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.2077</v>
+        <v>-0.0445</v>
       </c>
       <c r="P22" t="n">
-        <v>1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-2.2588</v>
       </c>
       <c r="R22" t="n">
-        <v>1.0267</v>
+        <v>2.0534</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.0894</v>
+        <v>-0.2393</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4534</v>
+        <v>-0.0622</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.636</v>
+        <v>-0.1771</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6591</v>
+        <v>-2.6838</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.0863</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6591</v>
+        <v>-2.5975</v>
       </c>
     </row>
     <row r="23">
@@ -2203,22 +2203,22 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.638999999999999</v>
+        <v>0.8479000000000014</v>
       </c>
       <c r="E23" t="n">
-        <v>4.1372</v>
+        <v>4.1374</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.776199999999999</v>
+        <v>-3.2894</v>
       </c>
       <c r="G23" t="n">
-        <v>3.736000000000001</v>
+        <v>3.736</v>
       </c>
       <c r="H23" t="n">
         <v>4.3146</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5787000000000005</v>
+        <v>-0.5787000000000001</v>
       </c>
       <c r="J23" t="n">
         <v>18.4204</v>
@@ -2236,10 +2236,10 @@
         <v>-7.0441</v>
       </c>
       <c r="O23" t="n">
-        <v>-7.640399999999999</v>
+        <v>-7.6404</v>
       </c>
       <c r="P23" t="n">
-        <v>8.213699999999999</v>
+        <v>8.213700000000001</v>
       </c>
       <c r="Q23" t="n">
         <v>-16.4274</v>
@@ -2248,19 +2248,19 @@
         <v>24.641</v>
       </c>
       <c r="S23" t="n">
-        <v>-11.991</v>
+        <v>-8.504600000000002</v>
       </c>
       <c r="T23" t="n">
         <v>-5.2127</v>
       </c>
       <c r="U23" t="n">
-        <v>-6.778300000000001</v>
+        <v>-3.291599999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-2.5974</v>
       </c>
       <c r="W23" t="n">
-        <v>7.357</v>
+        <v>7.357000000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-9.954600000000001</v>
